--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.96919528383978</v>
+        <v>12.66999423362397</v>
       </c>
       <c r="D2" t="n">
-        <v>77.95847288875787</v>
+        <v>12.66825184442315</v>
       </c>
       <c r="E2" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F2" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.10673770279315</v>
+        <v>12.69234487670389</v>
       </c>
       <c r="D3" t="n">
-        <v>78.07454273742059</v>
+        <v>12.68711319483084</v>
       </c>
       <c r="E3" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F3" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.45453378969469</v>
+        <v>9.336361740825387</v>
       </c>
       <c r="D4" t="n">
-        <v>57.512549594202</v>
+        <v>9.345789309057825</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F4" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.48707828592615</v>
+        <v>9.991650221462999</v>
       </c>
       <c r="D5" t="n">
-        <v>61.49164504288704</v>
+        <v>9.992392319469145</v>
       </c>
       <c r="E5" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F5" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.00715762076423</v>
+        <v>7.313663113374188</v>
       </c>
       <c r="D6" t="n">
-        <v>45.13776705226299</v>
+        <v>7.334887145992737</v>
       </c>
       <c r="E6" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F6" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.19061585422532</v>
+        <v>7.830975076311615</v>
       </c>
       <c r="D7" t="n">
-        <v>48.30618176646024</v>
+        <v>7.849754537049789</v>
       </c>
       <c r="E7" t="n">
-        <v>12.98996426418714</v>
+        <v>2.11086919293041</v>
       </c>
       <c r="F7" t="n">
-        <v>12.93091430101541</v>
+        <v>2.101273573915004</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
